--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45687</v>
+        <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1125,13 +1125,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1174,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1188,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45545</v>
+        <v>46013</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1204,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1247,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1261,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45929</v>
+        <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1277,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1320,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1334,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45629</v>
+        <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1350,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1393,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46090</v>
+        <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1423,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>11.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45093</v>
+        <v>44712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>11.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>46090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46013</v>
+        <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45993</v>
+        <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45397</v>
+        <v>45638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44712</v>
+        <v>44684</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>11.2</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46056</v>
+        <v>45629</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45629</v>
+        <v>46276</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45233</v>
+        <v>46234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46234</v>
+        <v>45295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44684</v>
+        <v>45434</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45295</v>
+        <v>45093</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2367,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2410,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2424,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45638</v>
+        <v>45397</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2440,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2488,7 +2483,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2502,10 +2497,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46276</v>
+        <v>45687</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2517,8 +2512,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45545</v>
+        <v>45233</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46013</v>
+        <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45993</v>
+        <v>46090</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46056</v>
+        <v>45687</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1344,8 +1344,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1405,7 +1410,7 @@
         <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1461,7 +1466,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44712</v>
+        <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>11.2</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46090</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45629</v>
+        <v>45093</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45229</v>
+        <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45638</v>
+        <v>45993</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44684</v>
+        <v>46056</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45629</v>
+        <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45233</v>
+        <v>45397</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46276</v>
+        <v>44712</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46234</v>
+        <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45295</v>
+        <v>45629</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45434</v>
+        <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45093</v>
+        <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2367,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2410,7 +2415,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2424,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45397</v>
+        <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2440,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2483,7 +2488,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2497,10 +2502,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45687</v>
+        <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2512,13 +2517,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45233</v>
+        <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45545</v>
+        <v>46013</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46090</v>
+        <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45687</v>
+        <v>45993</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1344,13 +1344,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1410,7 +1405,7 @@
         <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1483,7 +1478,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>46056</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45093</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46013</v>
+        <v>46090</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>11.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45993</v>
+        <v>45638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46056</v>
+        <v>44684</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44684</v>
+        <v>45629</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45397</v>
+        <v>45233</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44712</v>
+        <v>45295</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>11.2</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2140,7 +2135,7 @@
         <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45629</v>
+        <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45295</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45638</v>
+        <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2371,8 +2366,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46013</v>
+        <v>45687</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1198,8 +1198,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1247,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1261,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44712</v>
+        <v>46090</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1277,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1320,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1334,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45993</v>
+        <v>45629</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1350,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1393,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45929</v>
+        <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1423,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1466,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45629</v>
+        <v>45929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46056</v>
+        <v>45397</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>44712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>11.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46090</v>
+        <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11.5</v>
+        <v>7.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45638</v>
+        <v>45629</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44684</v>
+        <v>45233</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45629</v>
+        <v>45229</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45233</v>
+        <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45295</v>
+        <v>46234</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45434</v>
+        <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45093</v>
+        <v>45993</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>44684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45687</v>
+        <v>46056</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2366,13 +2371,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46276</v>
+        <v>45295</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46234</v>
+        <v>45638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45687</v>
+        <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1198,13 +1198,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>11.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1247,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1261,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46090</v>
+        <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1277,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1320,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1334,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45629</v>
+        <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1350,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1393,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45093</v>
+        <v>45638</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1423,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45929</v>
+        <v>44684</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45397</v>
+        <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44712</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>11.2</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45629</v>
+        <v>45295</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45233</v>
+        <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45229</v>
+        <v>45993</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46276</v>
+        <v>46056</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46234</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46013</v>
+        <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45993</v>
+        <v>46090</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44684</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46056</v>
+        <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2371,8 +2366,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45295</v>
+        <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45638</v>
+        <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45638</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44684</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45233</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>45295</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45993</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>46056</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>46090</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45638</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44684</v>
+        <v>45229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45629</v>
+        <v>44684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45233</v>
+        <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45295</v>
+        <v>45993</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46013</v>
+        <v>45233</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45993</v>
+        <v>46056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46056</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45434</v>
+        <v>46090</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>11.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45093</v>
+        <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>7.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46090</v>
+        <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2281,7 +2281,7 @@
         <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 20202-2022</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44698</v>
+        <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 20202-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45545</v>
+        <v>44698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44712</v>
+        <v>45093</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>11.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45629</v>
+        <v>45545</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45929</v>
+        <v>45397</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45638</v>
+        <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45229</v>
+        <v>45929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44684</v>
+        <v>45434</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45629</v>
+        <v>45687</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1636,8 +1636,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46013</v>
+        <v>45629</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45993</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1843,7 +1848,7 @@
         <v>45233</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46056</v>
+        <v>46013</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>45993</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46090</v>
+        <v>46056</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45434</v>
+        <v>46090</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.3</v>
+        <v>11.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45093</v>
+        <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45687</v>
+        <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2366,13 +2371,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 20202-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45629</v>
+        <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 20202-2022</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44698</v>
+        <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45093</v>
+        <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>11.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45545</v>
+        <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45397</v>
+        <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44712</v>
+        <v>45638</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>11.2</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45929</v>
+        <v>45229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45434</v>
+        <v>44684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45687</v>
+        <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1636,13 +1636,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45629</v>
+        <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45993</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1848,7 +1843,7 @@
         <v>45233</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46013</v>
+        <v>46056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45993</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46056</v>
+        <v>46090</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46090</v>
+        <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>11.5</v>
+        <v>7.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44684</v>
+        <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45295</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45638</v>
+        <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2371,8 +2366,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45545</v>
+        <v>46013</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44712</v>
+        <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>11.2</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45629</v>
+        <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45929</v>
+        <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45638</v>
+        <v>45687</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1417,8 +1417,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1466,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45229</v>
+        <v>45929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44684</v>
+        <v>46090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1624,7 +1629,7 @@
         <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46013</v>
+        <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45993</v>
+        <v>45093</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45233</v>
+        <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46056</v>
+        <v>44712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>45434</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46090</v>
+        <v>45629</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45093</v>
+        <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>46234</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45687</v>
+        <v>44684</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2366,13 +2371,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46276</v>
+        <v>45295</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46234</v>
+        <v>45638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>46013</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45687</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45093</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>44712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45434</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45629</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45233</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>46234</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44684</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45295</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>46013</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45687</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45093</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>44712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45434</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45629</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45233</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>46234</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44684</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45295</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46013</v>
+        <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45545</v>
+        <v>45929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45993</v>
+        <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>11.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46056</v>
+        <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45687</v>
+        <v>45993</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1417,13 +1417,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45929</v>
+        <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46090</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45629</v>
+        <v>46056</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45229</v>
+        <v>46090</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45093</v>
+        <v>45638</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45397</v>
+        <v>44684</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44712</v>
+        <v>45629</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>11.2</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45629</v>
+        <v>45295</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45233</v>
+        <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46276</v>
+        <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46234</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44684</v>
+        <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2371,8 +2366,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45295</v>
+        <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45638</v>
+        <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45929</v>
+        <v>46013</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44712</v>
+        <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>11.2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46013</v>
+        <v>45687</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1344,8 +1344,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1393,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45993</v>
+        <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1423,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1466,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45629</v>
+        <v>46056</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46056</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1697,7 +1702,7 @@
         <v>46090</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45638</v>
+        <v>45093</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44684</v>
+        <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45629</v>
+        <v>44712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45233</v>
+        <v>45434</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45295</v>
+        <v>45629</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45093</v>
+        <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45687</v>
+        <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2366,13 +2371,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46276</v>
+        <v>45638</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45545</v>
+        <v>45233</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46013</v>
+        <v>45629</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45993</v>
+        <v>45295</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45687</v>
+        <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1344,13 +1344,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1393,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45929</v>
+        <v>45093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1423,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46056</v>
+        <v>45638</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45629</v>
+        <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45397</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46090</v>
+        <v>45687</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1714,8 +1709,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45093</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45397</v>
+        <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>44712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45434</v>
+        <v>45929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45629</v>
+        <v>45229</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45233</v>
+        <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44684</v>
+        <v>45993</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45295</v>
+        <v>46056</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46276</v>
+        <v>46090</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45638</v>
+        <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>46234</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45233</v>
+        <v>46013</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45629</v>
+        <v>45993</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45295</v>
+        <v>45545</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45434</v>
+        <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45093</v>
+        <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45638</v>
+        <v>45687</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1490,8 +1490,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 12510-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45545</v>
+        <v>46090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45397</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45687</v>
+        <v>45629</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1709,13 +1714,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45093</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45629</v>
+        <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>44712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45929</v>
+        <v>45434</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46013</v>
+        <v>45233</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45993</v>
+        <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46056</v>
+        <v>44684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46090</v>
+        <v>45295</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.5</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46276</v>
+        <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46234</v>
+        <v>45638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE26"/>
+  <dimension ref="A1:AE25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>46013</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45993</v>
+        <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45545</v>
+        <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45687</v>
+        <v>44712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1490,13 +1490,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>11.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12510-2026</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46090</v>
+        <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1629,7 +1624,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45629</v>
+        <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45093</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45397</v>
+        <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44712</v>
+        <v>45233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>11.2</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45434</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45629</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45233</v>
+        <v>46276</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46276</v>
+        <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44684</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45295</v>
+        <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2371,8 +2366,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>A 32099-2026</t>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2484,79 +2484,6 @@
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 59471-2024</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45638</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>BJUV</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>46013</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>46276</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>46013</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>46276</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46013</v>
+        <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45545</v>
+        <v>45687</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1198,8 +1198,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1247,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1261,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45993</v>
+        <v>46056</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1277,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1320,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1334,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46056</v>
+        <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1350,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1393,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45929</v>
+        <v>45629</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1423,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1466,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44712</v>
+        <v>45093</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>11.2</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45629</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>46013</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45638</v>
+        <v>45993</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45397</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45629</v>
+        <v>44712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45233</v>
+        <v>45434</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46276</v>
+        <v>44684</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45093</v>
+        <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45687</v>
+        <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2366,13 +2371,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45687</v>
+        <v>46013</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1198,13 +1198,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1247,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1261,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46056</v>
+        <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1277,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1320,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1334,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45929</v>
+        <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1350,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>11.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1393,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45629</v>
+        <v>46056</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1423,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45093</v>
+        <v>45929</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46013</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45993</v>
+        <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45397</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44712</v>
+        <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>11.2</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45629</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45233</v>
+        <v>46276</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44684</v>
+        <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46276</v>
+        <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45295</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45638</v>
+        <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2371,8 +2366,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45545</v>
+        <v>45093</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46013</v>
+        <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45993</v>
+        <v>45397</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46056</v>
+        <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45929</v>
+        <v>45434</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45687</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1636,8 +1636,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45638</v>
+        <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45233</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1843,7 +1848,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45233</v>
+        <v>46013</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>45993</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46276</v>
+        <v>46056</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45434</v>
+        <v>44684</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45093</v>
+        <v>45295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>45638</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45687</v>
+        <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2366,13 +2371,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45093</v>
+        <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45545</v>
+        <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>11.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45397</v>
+        <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44712</v>
+        <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>11.2</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45929</v>
+        <v>45638</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45434</v>
+        <v>45229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45629</v>
+        <v>44684</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45687</v>
+        <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1636,13 +1636,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45229</v>
+        <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45233</v>
+        <v>45993</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45629</v>
+        <v>45233</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46013</v>
+        <v>46056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45993</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46056</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44684</v>
+        <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45295</v>
+        <v>45397</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45638</v>
+        <v>45687</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2298,8 +2293,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45545</v>
+        <v>45295</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44712</v>
+        <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>11.2</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45629</v>
+        <v>45397</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45929</v>
+        <v>45638</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45638</v>
+        <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45229</v>
+        <v>45434</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>7.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44684</v>
+        <v>45687</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,8 +1563,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1624,7 +1629,7 @@
         <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46013</v>
+        <v>45929</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45993</v>
+        <v>45233</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45233</v>
+        <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46056</v>
+        <v>45093</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>45229</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45434</v>
+        <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45093</v>
+        <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45397</v>
+        <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45687</v>
+        <v>46056</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2293,13 +2298,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45295</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45397</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45638</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45434</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45687</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45929</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45233</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45093</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45229</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>46056</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45295</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45397</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45638</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45434</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45687</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45929</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45233</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45093</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45229</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45993</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>46056</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45295</v>
+        <v>45929</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45545</v>
+        <v>45229</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45397</v>
+        <v>46276</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45638</v>
+        <v>46013</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44712</v>
+        <v>45993</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>11.2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45434</v>
+        <v>46056</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45687</v>
+        <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,13 +1563,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45629</v>
+        <v>46234</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45929</v>
+        <v>44712</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>11.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45233</v>
+        <v>45629</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45629</v>
+        <v>45638</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45093</v>
+        <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46013</v>
+        <v>45233</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45993</v>
+        <v>45295</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44684</v>
+        <v>45434</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46056</v>
+        <v>45093</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46276</v>
+        <v>45397</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2367,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2410,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2424,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46234</v>
+        <v>45687</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2444,8 +2439,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45929</v>
+        <v>46013</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45229</v>
+        <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46276</v>
+        <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46013</v>
+        <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45993</v>
+        <v>45687</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1417,8 +1417,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1478,7 +1483,7 @@
         <v>46056</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45545</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46234</v>
+        <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44712</v>
+        <v>45093</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11.2</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45629</v>
+        <v>45397</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45638</v>
+        <v>44712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44684</v>
+        <v>45434</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1989,7 +1994,7 @@
         <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2062,7 +2067,7 @@
         <v>45233</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45295</v>
+        <v>44684</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45434</v>
+        <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45093</v>
+        <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45397</v>
+        <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2367,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2410,7 +2415,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2424,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45687</v>
+        <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2439,13 +2444,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46013</v>
+        <v>45638</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45993</v>
+        <v>45929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45929</v>
+        <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>11.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45687</v>
+        <v>44684</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1417,13 +1417,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46056</v>
+        <v>45229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45629</v>
+        <v>46013</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45093</v>
+        <v>45629</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45397</v>
+        <v>45993</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44712</v>
+        <v>46056</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>11.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45629</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45233</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44684</v>
+        <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2213,7 +2208,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45295</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45638</v>
+        <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2371,8 +2366,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45638</v>
+        <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45545</v>
+        <v>45397</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45929</v>
+        <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>11.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44712</v>
+        <v>45687</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1344,8 +1344,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>11.2</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1393,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44684</v>
+        <v>45434</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1423,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1466,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1551,7 +1556,7 @@
         <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46013</v>
+        <v>45233</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45629</v>
+        <v>45093</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45993</v>
+        <v>45929</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46056</v>
+        <v>44684</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45233</v>
+        <v>45295</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45434</v>
+        <v>45638</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45093</v>
+        <v>45229</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46276</v>
+        <v>46234</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>46013</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45687</v>
+        <v>45993</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2366,13 +2371,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46234</v>
+        <v>46056</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45397</v>
+        <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>11.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44712</v>
+        <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>11.2</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45687</v>
+        <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1344,13 +1344,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1393,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45434</v>
+        <v>45638</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1423,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45629</v>
+        <v>44684</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45629</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45233</v>
+        <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45093</v>
+        <v>45233</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45929</v>
+        <v>46013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44684</v>
+        <v>45993</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45295</v>
+        <v>46056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46276</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45638</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45229</v>
+        <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46234</v>
+        <v>45397</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46013</v>
+        <v>45687</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2298,8 +2293,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45993</v>
+        <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46056</v>
+        <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45638</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44684</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45233</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45993</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>46056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45397</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45687</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45638</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44684</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45233</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45993</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>46056</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45397</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45687</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>46276</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44712</v>
+        <v>45687</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1198,8 +1198,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>11.2</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1247,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1259,7 +1264,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1277,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1320,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1334,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45929</v>
+        <v>45093</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1350,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1393,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45638</v>
+        <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1423,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1466,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44684</v>
+        <v>45397</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>44712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>11.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45629</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45233</v>
+        <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46013</v>
+        <v>45629</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45993</v>
+        <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46056</v>
+        <v>45993</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>46056</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45434</v>
+        <v>45233</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45093</v>
+        <v>44684</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45397</v>
+        <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45687</v>
+        <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2293,13 +2298,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46276</v>
+        <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45687</v>
+        <v>46013</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1198,13 +1198,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1247,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1261,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45629</v>
+        <v>45993</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1277,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1320,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1334,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45093</v>
+        <v>46056</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1350,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1410,7 +1405,7 @@
         <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45397</v>
+        <v>44712</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1496,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.8</v>
+        <v>11.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44712</v>
+        <v>45629</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>11.2</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1629,7 +1624,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45434</v>
+        <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45629</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46013</v>
+        <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45993</v>
+        <v>45233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46056</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45233</v>
+        <v>46276</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44684</v>
+        <v>45434</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46276</v>
+        <v>45093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45295</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45638</v>
+        <v>46234</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2367,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2410,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2424,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46234</v>
+        <v>45687</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2444,8 +2439,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>46013</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45993</v>
+        <v>45929</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46056</v>
+        <v>45687</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1344,8 +1344,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1393,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45929</v>
+        <v>45993</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1423,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1466,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44712</v>
+        <v>45229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1496,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>11.2</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45629</v>
+        <v>46056</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45638</v>
+        <v>45093</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45397</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45629</v>
+        <v>44712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45233</v>
+        <v>45434</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46276</v>
+        <v>45233</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45434</v>
+        <v>44684</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2205,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45093</v>
+        <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46234</v>
+        <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2367,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2410,7 +2415,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2424,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45687</v>
+        <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2439,13 +2444,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45545</v>
+        <v>45295</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46013</v>
+        <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45929</v>
+        <v>45093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45687</v>
+        <v>45929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1344,13 +1344,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1393,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45993</v>
+        <v>45397</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1423,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1466,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45229</v>
+        <v>45687</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1495,8 +1490,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46056</v>
+        <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45629</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45093</v>
+        <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45397</v>
+        <v>45993</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44712</v>
+        <v>46056</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>11.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45434</v>
+        <v>44712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.3</v>
+        <v>11.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45629</v>
+        <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45233</v>
+        <v>45629</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44684</v>
+        <v>45638</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46276</v>
+        <v>46234</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45295</v>
+        <v>44684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45638</v>
+        <v>45629</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46234</v>
+        <v>45233</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45295</v>
+        <v>44684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45434</v>
+        <v>45929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45093</v>
+        <v>45295</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45929</v>
+        <v>45638</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45397</v>
+        <v>45229</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45687</v>
+        <v>46013</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1490,13 +1490,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45545</v>
+        <v>45993</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46013</v>
+        <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45993</v>
+        <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46056</v>
+        <v>45687</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,8 +1855,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44712</v>
+        <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>11.2</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46276</v>
+        <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45629</v>
+        <v>45093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45638</v>
+        <v>45397</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46234</v>
+        <v>44712</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>11.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44684</v>
+        <v>45434</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2359,7 +2359,7 @@
         <v>45629</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>45233</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45295</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45638</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45229</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45993</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45687</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45397</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44712</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45434</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45629</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45233</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44684</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45929</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45295</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45638</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45229</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45993</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46056</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>46234</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45687</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45397</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44712</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45434</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45629</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45233</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44684</v>
+        <v>45929</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45929</v>
+        <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45295</v>
+        <v>45229</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45638</v>
+        <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>11.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45229</v>
+        <v>45629</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>46013</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45993</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45545</v>
+        <v>46056</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46056</v>
+        <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46234</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45687</v>
+        <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1855,13 +1855,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37514-2026</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46276</v>
+        <v>45233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45629</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45093</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45397</v>
+        <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44712</v>
+        <v>46234</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.2</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45434</v>
+        <v>45397</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2294,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2337,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2351,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45629</v>
+        <v>45687</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2371,8 +2366,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 37514-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45233</v>
+        <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 46998-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45929</v>
+        <v>45629</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45545</v>
+        <v>45638</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45229</v>
+        <v>45093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44712</v>
+        <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>11.2</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 46998-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45629</v>
+        <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46013</v>
+        <v>45687</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1490,8 +1490,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1539,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1553,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45993</v>
+        <v>45397</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1569,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46056</v>
+        <v>44712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1637,7 +1642,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45638</v>
+        <v>45434</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45629</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1783,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1826,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45629</v>
+        <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1856,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45233</v>
+        <v>46013</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1972,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45295</v>
+        <v>45993</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2045,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45434</v>
+        <v>46056</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2075,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2118,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2132,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45093</v>
+        <v>45233</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2208,7 +2213,7 @@
         <v>46234</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2264,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45397</v>
+        <v>44684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45687</v>
+        <v>45295</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2366,13 +2371,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45946</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 20202-2022</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44698</v>
+        <v>44684</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 20202-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45629</v>
+        <v>44698</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45638</v>
+        <v>45629</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45093</v>
+        <v>45233</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45545</v>
+        <v>45295</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45687</v>
+        <v>45434</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1490,13 +1490,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1539,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1553,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45397</v>
+        <v>45093</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1569,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 53218-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44712</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1642,7 +1637,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>11.2</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45434</v>
+        <v>45397</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45629</v>
+        <v>45687</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1787,8 +1782,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 53218-2023</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45229</v>
+        <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46013</v>
+        <v>45993</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45993</v>
+        <v>46056</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46056</v>
+        <v>45545</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45233</v>
+        <v>44712</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46234</v>
+        <v>45629</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44684</v>
+        <v>46234</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45295</v>
+        <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Översikt BJUV.xlsx
+++ b/Översikt BJUV.xlsx
@@ -601,7 +601,7 @@
         <v>45993</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 50759-2025</t>
+          <t>A 59876-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45946</v>
+        <v>45993</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -764,51 +764,51 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Gulsparv
-Dvärghäxört</t>
+          <t>Entita
+Röd glada</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 59876-2025</t>
+          <t>A 50759-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45993</v>
+        <v>45946</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -874,44 +874,44 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Röd glada</t>
+          <t>Gulsparv
+Dvärghäxört</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 59876-2025 artfynd.xlsx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/artfynd/A 50759-2025 artfynd.xlsx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 59876-2025 karta.png", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor/A 50759-2025 karta.png", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 59876-2025 georefererad karta.tif", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/kartor_geotiff/A 50759-2025 georefererad karta.tif", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 59876-2025 FSC-klagomål.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomål/A 50759-2025 FSC-klagomål.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 59876-2025 FSC-klagomål mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/klagomålsmail/A 50759-2025 FSC-klagomål mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 59876-2025 tillsynsbegäran.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsyn/A 50759-2025 tillsynsbegäran.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 59876-2025 tillsynsbegäran mail.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/tillsynsmail/A 50759-2025 tillsynsbegäran mail.docx", "A 50759-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 59876-2025 prioriterade fågelarter.docx", "A 59876-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1260/fåglar/A 50759-2025 prioriterade fågelarter.docx", "A 50759-2025")</f>
         <v/>
       </c>
     </row>
@@ -935,7 +935,7 @@
         <v>45356</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 18118-2022</t>
+          <t>A 20202-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44684</v>
+        <v>44698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 20202-2022</t>
+          <t>A 38182-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44698</v>
+        <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 57391-2024</t>
+          <t>A 63548-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45629</v>
+        <v>46013</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 54557-2023</t>
+          <t>A 22256-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45233</v>
+        <v>44712</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 325-2024</t>
+          <t>A 59877-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45295</v>
+        <v>45993</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>45929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20054-2024</t>
+          <t>A 57394-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45434</v>
+        <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 26708-2023</t>
+          <t>A 6684-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45093</v>
+        <v>46056</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 14674-2024</t>
+          <t>A 59471-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45397</v>
+        <v>45638</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4574-2025</t>
+          <t>A 18118-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45687</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1782,13 +1782,8 @@
           <t>BJUV</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1826,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 63548-2025</t>
+          <t>A 57391-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46013</v>
+        <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1856,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1899,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59877-2025</t>
+          <t>A 54557-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45993</v>
+        <v>45233</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1929,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1972,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6684-2026</t>
+          <t>A 325-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46056</v>
+        <v>45295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2002,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2045,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38182-2024</t>
+          <t>A 20054-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45545</v>
+        <v>45434</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2075,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2118,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22256-2022</t>
+          <t>A 26708-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44712</v>
+        <v>45093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2153,7 +2148,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>11.2</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57394-2024</t>
+          <t>A 14674-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2210,10 +2205,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45629</v>
+        <v>45397</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2226,7 +2221,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2269,7 +2264,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32099-2026</t>
+          <t>A 4574-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46234</v>
+        <v>45687</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2298,8 +2293,13 @@
           <t>BJUV</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59471-2024</t>
+          <t>A 32099-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45638</v>
+        <v>46234</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>46276</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
